--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27382,6 +27382,60 @@
         <v>225.88</v>
       </c>
       <c r="G998" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="C999" t="n">
+        <v>227.82</v>
+      </c>
+      <c r="D999" t="n">
+        <v>232.66</v>
+      </c>
+      <c r="E999" t="n">
+        <v>224.56</v>
+      </c>
+      <c r="F999" t="n">
+        <v>226.23</v>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>243.24</v>
+      </c>
+      <c r="C1000" t="n">
+        <v>228.27</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>233.09</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>225.74</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>226.97</v>
+      </c>
+      <c r="G1000" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27398,7 +27452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1081"/>
+  <dimension ref="A1:B1083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38211,6 +38265,26 @@
       </c>
       <c r="B1081" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -38373,28 +38447,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5646197296548079</v>
+        <v>0.5620633933871174</v>
       </c>
       <c r="J2" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K2" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08892348136410244</v>
+        <v>0.08852772404388198</v>
       </c>
       <c r="M2" t="n">
-        <v>9.723410757781538</v>
+        <v>9.709934656815069</v>
       </c>
       <c r="N2" t="n">
-        <v>186.4565701076085</v>
+        <v>186.1644571261011</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6549101098326</v>
+        <v>13.64420965560487</v>
       </c>
       <c r="P2" t="n">
-        <v>233.9214183331246</v>
+        <v>233.9484932183998</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38445,28 +38519,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0441169725928417</v>
+        <v>0.04525685646549054</v>
       </c>
       <c r="J3" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K3" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01612036922308491</v>
+        <v>0.0169870743381394</v>
       </c>
       <c r="M3" t="n">
-        <v>2.215945096474912</v>
+        <v>2.217036146955191</v>
       </c>
       <c r="N3" t="n">
-        <v>6.781184876495846</v>
+        <v>6.783774642817906</v>
       </c>
       <c r="O3" t="n">
-        <v>2.604070827857001</v>
+        <v>2.604568033824017</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0102189253884</v>
+        <v>223.9981444448439</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38517,28 +38591,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1315269298913877</v>
+        <v>0.1321514273637698</v>
       </c>
       <c r="J4" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K4" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1540145347169739</v>
+        <v>0.1557402024069775</v>
       </c>
       <c r="M4" t="n">
-        <v>1.960650039988046</v>
+        <v>1.960014635525837</v>
       </c>
       <c r="N4" t="n">
-        <v>5.424475527303804</v>
+        <v>5.41852514349613</v>
       </c>
       <c r="O4" t="n">
-        <v>2.329050348812538</v>
+        <v>2.327772571256937</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7588653647988</v>
+        <v>227.7522498768894</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38589,28 +38663,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1124417518643349</v>
+        <v>0.1137313057611502</v>
       </c>
       <c r="J5" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K5" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07570875536265897</v>
+        <v>0.07747768935130139</v>
       </c>
       <c r="M5" t="n">
-        <v>2.440682938384052</v>
+        <v>2.442624252364325</v>
       </c>
       <c r="N5" t="n">
-        <v>8.811404415117785</v>
+        <v>8.814999065123288</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96840098624121</v>
+        <v>2.969006410421387</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8936492632508</v>
+        <v>218.8799880260418</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38661,28 +38735,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2449004270726273</v>
+        <v>0.2461153708516884</v>
       </c>
       <c r="J6" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="K6" t="n">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3142710420680769</v>
+        <v>0.316870246104143</v>
       </c>
       <c r="M6" t="n">
-        <v>2.245768736575076</v>
+        <v>2.247506472636288</v>
       </c>
       <c r="N6" t="n">
-        <v>7.470581434227245</v>
+        <v>7.474139821172471</v>
       </c>
       <c r="O6" t="n">
-        <v>2.733236439503038</v>
+        <v>2.733887309523286</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9435703903134</v>
+        <v>216.9307003071755</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38720,7 +38794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75649,6 +75723,80 @@
         </is>
       </c>
     </row>
+    <row r="999">
+      <c r="A999" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>-41.04293049286453,173.02013206881125</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>-41.04240310662414,173.01946061742555</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>-41.04182676215621,173.0190337253601</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>-41.04118454268771,173.01859100395103</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>-41.040509798994194,173.01825630392423</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>-41.04292630261328,173.02014039090201</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>-41.04240086187252,173.01946507567584</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>-41.041825325736966,173.0190384766869</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>-41.04118059752756,173.01860404057686</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>-41.04050732627308,173.01826448007108</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27436,6 +27436,114 @@
         <v>226.97</v>
       </c>
       <c r="G1000" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>241.57</v>
+      </c>
+      <c r="C1001" t="n">
+        <v>228.17</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>233.16</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>225.76</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>227.33</v>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>241.57</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>228.16</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>233.05</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>225.7</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>227.16</v>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>240.54</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>228.52</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>226.04</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>227.51</v>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>241.61</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>228.63</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>233.38</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>226.11</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>227.37</v>
+      </c>
+      <c r="G1004" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27452,7 +27560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1083"/>
+  <dimension ref="A1:B1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38285,6 +38393,46 @@
       </c>
       <c r="B1083" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>
@@ -38447,28 +38595,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5620633933871174</v>
+        <v>0.5557955511617592</v>
       </c>
       <c r="J2" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K2" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08852772404388198</v>
+        <v>0.08736327131500565</v>
       </c>
       <c r="M2" t="n">
-        <v>9.709934656815069</v>
+        <v>9.685760367393025</v>
       </c>
       <c r="N2" t="n">
-        <v>186.1644571261011</v>
+        <v>185.6666234934384</v>
       </c>
       <c r="O2" t="n">
-        <v>13.64420965560487</v>
+        <v>13.62595403975217</v>
       </c>
       <c r="P2" t="n">
-        <v>233.9484932183998</v>
+        <v>234.0150762382389</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38519,28 +38667,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04525685646549054</v>
+        <v>0.04776182814863186</v>
       </c>
       <c r="J3" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K3" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0169870743381394</v>
+        <v>0.01894729561829178</v>
       </c>
       <c r="M3" t="n">
-        <v>2.217036146955191</v>
+        <v>2.220299985345391</v>
       </c>
       <c r="N3" t="n">
-        <v>6.783774642817906</v>
+        <v>6.795816501200363</v>
       </c>
       <c r="O3" t="n">
-        <v>2.604568033824017</v>
+        <v>2.60687868939089</v>
       </c>
       <c r="P3" t="n">
-        <v>223.9981444448439</v>
+        <v>223.9715327474209</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38591,28 +38739,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1321514273637698</v>
+        <v>0.133644474036209</v>
       </c>
       <c r="J4" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K4" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1557402024069775</v>
+        <v>0.1596087837911555</v>
       </c>
       <c r="M4" t="n">
-        <v>1.960014635525837</v>
+        <v>1.960074999552653</v>
       </c>
       <c r="N4" t="n">
-        <v>5.41852514349613</v>
+        <v>5.410798745282078</v>
       </c>
       <c r="O4" t="n">
-        <v>2.327772571256937</v>
+        <v>2.326112367294856</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7522498768894</v>
+        <v>227.736388561143</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38663,28 +38811,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1137313057611502</v>
+        <v>0.1168663812630617</v>
       </c>
       <c r="J5" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K5" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07747768935130139</v>
+        <v>0.08162710774621307</v>
       </c>
       <c r="M5" t="n">
-        <v>2.442624252364325</v>
+        <v>2.449330091436333</v>
       </c>
       <c r="N5" t="n">
-        <v>8.814999065123288</v>
+        <v>8.840941003834448</v>
       </c>
       <c r="O5" t="n">
-        <v>2.969006410421387</v>
+        <v>2.973371992172262</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8799880260418</v>
+        <v>218.8466832776751</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38735,28 +38883,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2461153708516884</v>
+        <v>0.2490916043728163</v>
       </c>
       <c r="J6" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="K6" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.316870246104143</v>
+        <v>0.3225043520673406</v>
       </c>
       <c r="M6" t="n">
-        <v>2.247506472636288</v>
+        <v>2.253837432129974</v>
       </c>
       <c r="N6" t="n">
-        <v>7.474139821172471</v>
+        <v>7.499352402907379</v>
       </c>
       <c r="O6" t="n">
-        <v>2.733887309523286</v>
+        <v>2.738494550461508</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9307003071755</v>
+        <v>216.8990838612773</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38794,7 +38942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75797,6 +75945,154 @@
         </is>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>-41.042934633231226,173.02012384579194</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>-41.042401360706236,173.01946408495357</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>-41.04182509190126,173.01903925015867</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>-41.04118053066043,173.0186042615366</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>-41.04050612332747,173.0182684576558</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>-41.042934633231226,173.02012384579194</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>-41.04240141058961,173.01946398588134</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>-41.04182545935737,173.019038034703</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>-41.04118073126181,173.01860359865736</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>-41.040506691385126,173.01826657935192</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>-41.04293977127584,173.02011364132076</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>-41.04239961478823,173.01946755248144</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>-41.041824757850236,173.01904035511834</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>-41.0411795945205,173.01860735497303</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>-41.040505521854605,173.01827044644813</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>-41.0429344336955,173.02012424208206</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>-41.04239906607112,173.01946864227585</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>-41.041824356989004,173.01904168106995</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>-41.04117936048551,173.0186081283321</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>-41.040505989666826,173.01826889960967</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1004"/>
+  <dimension ref="A1:G1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27544,6 +27544,87 @@
         <v>227.37</v>
       </c>
       <c r="G1004" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>241.12</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>228.84</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>233.64</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>226.21</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>226.89</v>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>241.53</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>228.85</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>233.61</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>226.75</v>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>240.72</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>228.61</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>233.59</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>225.12</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>226.27</v>
+      </c>
+      <c r="G1007" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27560,7 +27641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1087"/>
+  <dimension ref="A1:B1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38433,6 +38514,36 @@
       </c>
       <c r="B1087" t="n">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -38595,28 +38706,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5557955511617592</v>
+        <v>0.5510187098512744</v>
       </c>
       <c r="J2" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K2" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08736327131500565</v>
+        <v>0.08646135198207205</v>
       </c>
       <c r="M2" t="n">
-        <v>9.685760367393025</v>
+        <v>9.667940311456972</v>
       </c>
       <c r="N2" t="n">
-        <v>185.6666234934384</v>
+        <v>185.3029662790557</v>
       </c>
       <c r="O2" t="n">
-        <v>13.62595403975217</v>
+        <v>13.6126032146337</v>
       </c>
       <c r="P2" t="n">
-        <v>234.0150762382389</v>
+        <v>234.0660038871712</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38667,28 +38778,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04776182814863186</v>
+        <v>0.04984612438179772</v>
       </c>
       <c r="J3" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K3" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01894729561829178</v>
+        <v>0.02063461416989698</v>
       </c>
       <c r="M3" t="n">
-        <v>2.220299985345391</v>
+        <v>2.223770043701382</v>
       </c>
       <c r="N3" t="n">
-        <v>6.795816501200363</v>
+        <v>6.811707153687711</v>
       </c>
       <c r="O3" t="n">
-        <v>2.60687868939089</v>
+        <v>2.609924741000727</v>
       </c>
       <c r="P3" t="n">
-        <v>223.9715327474209</v>
+        <v>223.9493118887189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38739,28 +38850,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.133644474036209</v>
+        <v>0.1349806046863498</v>
       </c>
       <c r="J4" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K4" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1596087837911555</v>
+        <v>0.1628642689269356</v>
       </c>
       <c r="M4" t="n">
-        <v>1.960074999552653</v>
+        <v>1.961295030192058</v>
       </c>
       <c r="N4" t="n">
-        <v>5.410798745282078</v>
+        <v>5.409505677639218</v>
       </c>
       <c r="O4" t="n">
-        <v>2.326112367294856</v>
+        <v>2.325834404603909</v>
       </c>
       <c r="P4" t="n">
-        <v>227.736388561143</v>
+        <v>227.7221438206726</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38811,28 +38922,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1168663812630617</v>
+        <v>0.1190778498763217</v>
       </c>
       <c r="J5" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K5" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08162710774621307</v>
+        <v>0.08465637904832901</v>
       </c>
       <c r="M5" t="n">
-        <v>2.449330091436333</v>
+        <v>2.453637376804766</v>
       </c>
       <c r="N5" t="n">
-        <v>8.840941003834448</v>
+        <v>8.855869664889351</v>
       </c>
       <c r="O5" t="n">
-        <v>2.973371992172262</v>
+        <v>2.975881325740217</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8466832776751</v>
+        <v>218.8231074559253</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38883,28 +38994,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2490916043728163</v>
+        <v>0.2508558703897836</v>
       </c>
       <c r="J6" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K6" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3225043520673406</v>
+        <v>0.3263522931004655</v>
       </c>
       <c r="M6" t="n">
-        <v>2.253837432129974</v>
+        <v>2.256197458909564</v>
       </c>
       <c r="N6" t="n">
-        <v>7.499352402907379</v>
+        <v>7.503078351742496</v>
       </c>
       <c r="O6" t="n">
-        <v>2.738494550461508</v>
+        <v>2.739174757430145</v>
       </c>
       <c r="P6" t="n">
-        <v>216.8990838612773</v>
+        <v>216.880275293078</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38942,7 +39053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1004"/>
+  <dimension ref="A1:G1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76093,6 +76204,117 @@
         </is>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>-41.042936878008106,173.020119387528</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>-41.042398018520245,173.01947072279245</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>-41.04182348845625,173.01904455396505</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>-41.0411790261498,173.01860923313077</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>-41.04050759359431,173.01826359616334</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>-41.04293483276696,173.02012344950182</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>-41.04239796863686,173.01947082186467</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>-41.041823588671576,173.01904422247713</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>-41.0411801294576,173.01860558729507</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>-41.040508061406435,173.0182620493248</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>-41.04293887336519,173.0201154246265</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>-41.04239916583787,173.0194684441314</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>-41.0418236554818,173.01904400148524</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>-41.041182670408496,173.0185971908245</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>-41.0405096653336,173.01825674587815</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
